--- a/web/public/forms/gy-byeongyeong.xlsx
+++ b/web/public/forms/gy-byeongyeong.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경계약서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'변경계약서'!$A$1:$X$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0;[Red]-#,##0;0"/>
+    <numFmt numFmtId="167" formatCode="yyyy. m. d."/>
+    <numFmt numFmtId="168" formatCode="#,##0&quot;일&quot;;[Red]-#,##0&quot;일&quot;;0&quot;일&quot;"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,32 +40,59 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +101,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +125,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,35 +150,68 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -533,15 +607,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -565,7 +639,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -595,7 +669,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="7" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -625,7 +699,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -655,7 +729,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -676,7 +750,7 @@
     </row>
     <row r="9" ht="6" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
@@ -686,7 +760,7 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>당초</t>
         </is>
@@ -696,7 +770,7 @@
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="5" t="n"/>
       <c r="L10" s="5" t="n"/>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>변경</t>
         </is>
@@ -706,7 +780,7 @@
       <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="n"/>
       <c r="R10" s="5" t="n"/>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="8" t="inlineStr">
         <is>
           <t>증감</t>
         </is>
@@ -718,25 +792,32 @@
       <c r="X10" s="5" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>계약금액</t>
+        </is>
+      </c>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="8" t="inlineStr"/>
+      <c r="G11" s="10" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="n"/>
       <c r="L11" s="5" t="n"/>
-      <c r="M11" s="8" t="inlineStr"/>
+      <c r="M11" s="10" t="n"/>
       <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="n"/>
       <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="n"/>
       <c r="R11" s="5" t="n"/>
-      <c r="S11" s="8" t="inlineStr"/>
+      <c r="S11" s="11">
+        <f>IF(OR(G11="",M11=""),"",M11-G11)</f>
+        <v/>
+      </c>
       <c r="T11" s="5" t="n"/>
       <c r="U11" s="5" t="n"/>
       <c r="V11" s="5" t="n"/>
@@ -744,25 +825,32 @@
       <c r="X11" s="5" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>준공일</t>
+        </is>
+      </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="8" t="inlineStr"/>
+      <c r="G12" s="12" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="n"/>
       <c r="L12" s="5" t="n"/>
-      <c r="M12" s="8" t="inlineStr"/>
+      <c r="M12" s="12" t="n"/>
       <c r="N12" s="5" t="n"/>
       <c r="O12" s="5" t="n"/>
       <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="n"/>
       <c r="R12" s="5" t="n"/>
-      <c r="S12" s="8" t="inlineStr"/>
+      <c r="S12" s="13">
+        <f>IF(OR(G12="",M12=""),"",M12-G12)</f>
+        <v/>
+      </c>
       <c r="T12" s="5" t="n"/>
       <c r="U12" s="5" t="n"/>
       <c r="V12" s="5" t="n"/>
@@ -770,25 +858,29 @@
       <c r="X12" s="5" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr"/>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>공사 내용</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="8" t="inlineStr"/>
+      <c r="G13" s="6" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="n"/>
       <c r="L13" s="5" t="n"/>
-      <c r="M13" s="8" t="inlineStr"/>
+      <c r="M13" s="6" t="n"/>
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
       <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
-      <c r="S13" s="8" t="inlineStr"/>
+      <c r="S13" s="6" t="n"/>
       <c r="T13" s="5" t="n"/>
       <c r="U13" s="5" t="n"/>
       <c r="V13" s="5" t="n"/>
@@ -796,25 +888,25 @@
       <c r="X13" s="5" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="8" t="inlineStr"/>
+      <c r="G14" s="9" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n"/>
-      <c r="M14" s="8" t="inlineStr"/>
+      <c r="M14" s="9" t="n"/>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
       <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
-      <c r="S14" s="8" t="inlineStr"/>
+      <c r="S14" s="9" t="n"/>
       <c r="T14" s="5" t="n"/>
       <c r="U14" s="5" t="n"/>
       <c r="V14" s="5" t="n"/>
@@ -823,7 +915,7 @@
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>※ 구분: 계약금액 / 공사기간 / 공사 내용</t>
         </is>
@@ -831,14 +923,14 @@
     </row>
     <row r="17" ht="6" customHeight="1"/>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>제1조 (변경 사유)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">                                                                 </t>
         </is>
@@ -846,14 +938,14 @@
     </row>
     <row r="20" ht="4" customHeight="1"/>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>제2조 (변경 내용)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="43.5" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>위 표에 적은 바와 같이 계약 내용을 변경한다. 세부 내용은 별첨 변경 산출내역서에 따른다.</t>
         </is>
@@ -861,14 +953,14 @@
     </row>
     <row r="23" ht="4" customHeight="1"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>제3조 (변경 후 계약금액)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="43.5" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>변경 후 계약금액은 위 표에 적은 금액으로 하며, 그 밖의 사항은 당초 계약에 따른다.</t>
         </is>
@@ -876,14 +968,14 @@
     </row>
     <row r="26" ht="4" customHeight="1"/>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>제4조 (공사기간)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="43.5" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>공사기간은 위 표에 적은 바와 같이 변경한다. 기간이 변경되지 아니하는 경우 당초 기간을 유지한다.</t>
         </is>
@@ -891,14 +983,14 @@
     </row>
     <row r="29" ht="4" customHeight="1"/>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>제5조 (효력)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="29" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>이 변경계약에서 정하지 아니한 사항은 당초 계약의 내용에 따른다.</t>
         </is>
@@ -906,8 +998,8 @@
     </row>
     <row r="32" ht="4" customHeight="1"/>
     <row r="33" ht="6" customHeight="1"/>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>이 변경계약을 증명하기 위하여 2통을 작성하여 갑과 을이 각각 기명날인한 후 1통씩 보관한다.</t>
         </is>
@@ -915,13 +1007,13 @@
     </row>
     <row r="35" ht="6" customHeight="1"/>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
       <c r="B36" s="5" t="n"/>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>상호(성명)</t>
         </is>
@@ -930,7 +1022,7 @@
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>사업자등록번호</t>
         </is>
@@ -938,14 +1030,14 @@
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="5" t="n"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="L36" s="8" t="inlineStr">
         <is>
           <t>대표자</t>
         </is>
       </c>
       <c r="M36" s="5" t="n"/>
       <c r="N36" s="5" t="n"/>
-      <c r="O36" s="7" t="inlineStr">
+      <c r="O36" s="8" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
@@ -956,7 +1048,7 @@
       <c r="S36" s="5" t="n"/>
       <c r="T36" s="5" t="n"/>
       <c r="U36" s="5" t="n"/>
-      <c r="V36" s="7" t="inlineStr">
+      <c r="V36" s="8" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
@@ -965,60 +1057,68 @@
       <c r="X36" s="5" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="8" t="inlineStr"/>
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>갑</t>
+        </is>
+      </c>
       <c r="B37" s="5" t="n"/>
-      <c r="C37" s="8" t="inlineStr"/>
+      <c r="C37" s="17" t="n"/>
       <c r="D37" s="5" t="n"/>
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
-      <c r="H37" s="8" t="inlineStr"/>
+      <c r="H37" s="17" t="n"/>
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="5" t="n"/>
       <c r="K37" s="5" t="n"/>
-      <c r="L37" s="8" t="inlineStr"/>
+      <c r="L37" s="17" t="n"/>
       <c r="M37" s="5" t="n"/>
       <c r="N37" s="5" t="n"/>
-      <c r="O37" s="8" t="inlineStr"/>
+      <c r="O37" s="9" t="n"/>
       <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="n"/>
       <c r="R37" s="5" t="n"/>
       <c r="S37" s="5" t="n"/>
       <c r="T37" s="5" t="n"/>
       <c r="U37" s="5" t="n"/>
-      <c r="V37" s="8" t="inlineStr"/>
+      <c r="V37" s="17" t="n"/>
       <c r="W37" s="5" t="n"/>
       <c r="X37" s="5" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="8" t="inlineStr"/>
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>을</t>
+        </is>
+      </c>
       <c r="B38" s="5" t="n"/>
-      <c r="C38" s="8" t="inlineStr"/>
+      <c r="C38" s="17" t="n"/>
       <c r="D38" s="5" t="n"/>
       <c r="E38" s="5" t="n"/>
       <c r="F38" s="5" t="n"/>
       <c r="G38" s="5" t="n"/>
-      <c r="H38" s="8" t="inlineStr"/>
+      <c r="H38" s="17" t="n"/>
       <c r="I38" s="5" t="n"/>
       <c r="J38" s="5" t="n"/>
       <c r="K38" s="5" t="n"/>
-      <c r="L38" s="8" t="inlineStr"/>
+      <c r="L38" s="17" t="n"/>
       <c r="M38" s="5" t="n"/>
       <c r="N38" s="5" t="n"/>
-      <c r="O38" s="8" t="inlineStr"/>
+      <c r="O38" s="9" t="n"/>
       <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="n"/>
       <c r="R38" s="5" t="n"/>
       <c r="S38" s="5" t="n"/>
       <c r="T38" s="5" t="n"/>
       <c r="U38" s="5" t="n"/>
-      <c r="V38" s="8" t="inlineStr"/>
+      <c r="V38" s="17" t="n"/>
       <c r="W38" s="5" t="n"/>
       <c r="X38" s="5" t="n"/>
     </row>
     <row r="39" ht="6" customHeight="1"/>
-    <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
         </is>
@@ -1027,58 +1127,71 @@
     <row r="41" ht="6" customHeight="1"/>
     <row r="42" ht="10" customHeight="1"/>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="K44" s="12" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="19" t="inlineStr"/>
+      <c r="K44" s="20" t="inlineStr">
         <is>
           <t>갑 (발주자·원사업자)</t>
         </is>
       </c>
-      <c r="S44" s="11" t="inlineStr">
+      <c r="Q44" s="21" t="n"/>
+      <c r="U44" s="22" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="K45" s="12" t="inlineStr">
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="19" t="inlineStr"/>
+      <c r="K45" s="20" t="inlineStr">
         <is>
           <t>을 (수급인·수급사업자)</t>
         </is>
       </c>
-      <c r="S45" s="11" t="inlineStr">
+      <c r="Q45" s="21" t="n"/>
+      <c r="U45" s="22" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="6" customHeight="1"/>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="19.5" customHeight="1">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="73">
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="G10:L10"/>
     <mergeCell ref="M10:R10"/>
     <mergeCell ref="S14:X14"/>
     <mergeCell ref="A16:X16"/>
     <mergeCell ref="G13:L13"/>
+    <mergeCell ref="K44:P44"/>
     <mergeCell ref="A25:X25"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="M13:R13"/>
     <mergeCell ref="S13:X13"/>
+    <mergeCell ref="Q45:T45"/>
     <mergeCell ref="M11:R11"/>
     <mergeCell ref="M12:R12"/>
     <mergeCell ref="A18:X18"/>
@@ -1090,26 +1203,27 @@
     <mergeCell ref="L38:N38"/>
     <mergeCell ref="V36:X36"/>
     <mergeCell ref="O37:U37"/>
+    <mergeCell ref="A44:J44"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="G14:L14"/>
+    <mergeCell ref="U44:X44"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="H38:K38"/>
-    <mergeCell ref="S45:X45"/>
-    <mergeCell ref="K44:R44"/>
     <mergeCell ref="A22:X22"/>
+    <mergeCell ref="A45:J45"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="M14:R14"/>
     <mergeCell ref="O36:U36"/>
+    <mergeCell ref="U45:X45"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A43:X43"/>
     <mergeCell ref="L36:N36"/>
     <mergeCell ref="V37:X37"/>
     <mergeCell ref="A28:X28"/>
     <mergeCell ref="A19:X19"/>
-    <mergeCell ref="S44:X44"/>
     <mergeCell ref="C36:G36"/>
     <mergeCell ref="G8:X8"/>
     <mergeCell ref="G12:L12"/>
@@ -1123,20 +1237,782 @@
     <mergeCell ref="A34:X34"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="V38:X38"/>
+    <mergeCell ref="A48:X48"/>
     <mergeCell ref="A24:X24"/>
     <mergeCell ref="C38:G38"/>
+    <mergeCell ref="K45:P45"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="L37:N37"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="C37:G37"/>
     <mergeCell ref="A49:X49"/>
     <mergeCell ref="M1:X1"/>
-    <mergeCell ref="K45:R45"/>
+    <mergeCell ref="Q44:T44"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="S11:X11"/>
     <mergeCell ref="H37:K37"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>변  경  계  약  서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  당초 계약일</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="7" t="n">
+        <v>46083</v>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  당초 계약번호</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>제2026-0312호</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  변경 차수</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>제1회</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="6" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>당초</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>증감</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>계약금액</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="10" t="n">
+        <v>963241000</v>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="10" t="n">
+        <v>1011891000</v>
+      </c>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="11">
+        <f>IF(OR(G11="",M11=""),"",M11-G11)</f>
+        <v/>
+      </c>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>준공일</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="12" t="n">
+        <v>46387</v>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="12" t="n">
+        <v>46407</v>
+      </c>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="13">
+        <f>IF(OR(G12="",M12=""),"",M12-G12)</f>
+        <v/>
+      </c>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n"/>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>공사 내용</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>배수관 L=820m</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>배수관 L=862m · 집수정 3곳 추가</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>배수관 42m 늘어남</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="9" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="9" t="n"/>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="5" t="n"/>
+      <c r="V14" s="5" t="n"/>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="6" customHeight="1"/>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>※ 구분: 계약금액 / 공사기간 / 공사 내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="6" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>제1조 (변경 사유)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="43.5" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>기존 배수관 노후로 연결 구간 42m 추가 교체와 집수정 3곳 신설(실정보고 제3호 · 설계변경 승인 2026. 6. 15.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="4" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>제2조 (변경 내용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="43.5" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>위 표에 적은 바와 같이 계약 내용을 변경한다. 세부 내용은 별첨 변경 산출내역서에 따른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="4" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>제3조 (변경 후 계약금액)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="43.5" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>변경 후 계약금액은 위 표에 적은 금액으로 하며, 그 밖의 사항은 당초 계약에 따른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="4" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>제4조 (공사기간)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="43.5" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>공사기간은 위 표에 적은 바와 같이 변경한다. 기간이 변경되지 아니하는 경우 당초 기간을 유지한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="4" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>제5조 (효력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="29" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>이 변경계약에서 정하지 아니한 사항은 당초 계약의 내용에 따른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="4" customHeight="1"/>
+    <row r="33" ht="6" customHeight="1"/>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>이 변경계약을 증명하기 위하여 2통을 작성하여 갑과 을이 각각 기명날인한 후 1통씩 보관한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="6" customHeight="1"/>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>상호(성명)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>사업자등록번호</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>대표자</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="n"/>
+      <c r="Q36" s="5" t="n"/>
+      <c r="R36" s="5" t="n"/>
+      <c r="S36" s="5" t="n"/>
+      <c r="T36" s="5" t="n"/>
+      <c r="U36" s="5" t="n"/>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="n"/>
+      <c r="X36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>갑</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>가나시</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>가나시장</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="9" t="inlineStr">
+        <is>
+          <t>가나시 시청로 1</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="n"/>
+      <c r="Q37" s="5" t="n"/>
+      <c r="R37" s="5" t="n"/>
+      <c r="S37" s="5" t="n"/>
+      <c r="T37" s="5" t="n"/>
+      <c r="U37" s="5" t="n"/>
+      <c r="V37" s="17" t="inlineStr">
+        <is>
+          <t>000-000-0000</t>
+        </is>
+      </c>
+      <c r="W37" s="5" t="n"/>
+      <c r="X37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>을</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>예시건설(주)</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="17" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="9" t="inlineStr">
+        <is>
+          <t>가나시 마바로 45, 2층</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="n"/>
+      <c r="Q38" s="5" t="n"/>
+      <c r="R38" s="5" t="n"/>
+      <c r="S38" s="5" t="n"/>
+      <c r="T38" s="5" t="n"/>
+      <c r="U38" s="5" t="n"/>
+      <c r="V38" s="17" t="inlineStr">
+        <is>
+          <t>000-000-0000</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="n"/>
+      <c r="X38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="6" customHeight="1"/>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="10" customHeight="1"/>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="18" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="19" t="inlineStr"/>
+      <c r="K44" s="20" t="inlineStr">
+        <is>
+          <t>갑 (발주자·원사업자)</t>
+        </is>
+      </c>
+      <c r="Q44" s="21" t="inlineStr">
+        <is>
+          <t>가나시장</t>
+        </is>
+      </c>
+      <c r="U44" s="22" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="19" t="inlineStr"/>
+      <c r="K45" s="20" t="inlineStr">
+        <is>
+          <t>을 (수급인·수급사업자)</t>
+        </is>
+      </c>
+      <c r="Q45" s="21" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="U45" s="22" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="6" customHeight="1"/>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="72">
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="M10:R10"/>
+    <mergeCell ref="S14:X14"/>
+    <mergeCell ref="A16:X16"/>
+    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="K44:P44"/>
+    <mergeCell ref="A25:X25"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="M13:R13"/>
+    <mergeCell ref="S13:X13"/>
+    <mergeCell ref="Q45:T45"/>
+    <mergeCell ref="M11:R11"/>
+    <mergeCell ref="M12:R12"/>
+    <mergeCell ref="A18:X18"/>
+    <mergeCell ref="A27:X27"/>
+    <mergeCell ref="O38:U38"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="A21:X21"/>
+    <mergeCell ref="S10:X10"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="O37:U37"/>
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="U44:X44"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="A22:X22"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="M14:R14"/>
+    <mergeCell ref="O36:U36"/>
+    <mergeCell ref="U45:X45"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A43:X43"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="V37:X37"/>
+    <mergeCell ref="A28:X28"/>
+    <mergeCell ref="A19:X19"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="G8:X8"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="A31:X31"/>
+    <mergeCell ref="A40:X40"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="S12:X12"/>
+    <mergeCell ref="A30:X30"/>
+    <mergeCell ref="A34:X34"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="V38:X38"/>
+    <mergeCell ref="A48:X48"/>
+    <mergeCell ref="A24:X24"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="K45:P45"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="Q44:T44"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="S11:X11"/>
+    <mergeCell ref="H37:K37"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/gy-byeongyeong.xlsx
+++ b/web/public/forms/gy-byeongyeong.xlsx
@@ -610,7 +610,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="24" t="inlineStr">

--- a/web/public/forms/gy-byeongyeong.xlsx
+++ b/web/public/forms/gy-byeongyeong.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경계약서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'변경계약서'!$A$1:$X$46</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -141,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -209,9 +207,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -814,10 +809,7 @@
       <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="n"/>
       <c r="R11" s="5" t="n"/>
-      <c r="S11" s="11">
-        <f>IF(OR(G11="",M11=""),"",M11-G11)</f>
-        <v/>
-      </c>
+      <c r="S11" s="11" t="n"/>
       <c r="T11" s="5" t="n"/>
       <c r="U11" s="5" t="n"/>
       <c r="V11" s="5" t="n"/>
@@ -847,10 +839,7 @@
       <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="n"/>
       <c r="R12" s="5" t="n"/>
-      <c r="S12" s="13">
-        <f>IF(OR(G12="",M12=""),"",M12-G12)</f>
-        <v/>
-      </c>
+      <c r="S12" s="13" t="n"/>
       <c r="T12" s="5" t="n"/>
       <c r="U12" s="5" t="n"/>
       <c r="V12" s="5" t="n"/>
@@ -1162,6 +1151,7 @@
       </c>
     </row>
     <row r="46" ht="6" customHeight="1"/>
+    <row r="47"/>
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="23" t="inlineStr">
         <is>
@@ -1256,763 +1246,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>변  경  계  약  서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  당초 계약일</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="n">
-        <v>46083</v>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  당초 계약번호</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>제2026-0312호</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  변경 차수</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>제1회</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="6" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>당초</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>변경</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t>증감</t>
-        </is>
-      </c>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>계약금액</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="10" t="n">
-        <v>963241000</v>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="10" t="n">
-        <v>1011891000</v>
-      </c>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="11">
-        <f>IF(OR(G11="",M11=""),"",M11-G11)</f>
-        <v/>
-      </c>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>준공일</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="12" t="n">
-        <v>46387</v>
-      </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="12" t="n">
-        <v>46407</v>
-      </c>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="13">
-        <f>IF(OR(G12="",M12=""),"",M12-G12)</f>
-        <v/>
-      </c>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>공사 내용</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>배수관 L=820m</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>배수관 L=862m · 집수정 3곳 추가</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>배수관 42m 늘어남</t>
-        </is>
-      </c>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="9" t="n"/>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="6" customHeight="1"/>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>※ 구분: 계약금액 / 공사기간 / 공사 내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="6" customHeight="1"/>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>제1조 (변경 사유)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>기존 배수관 노후로 연결 구간 42m 추가 교체와 집수정 3곳 신설(실정보고 제3호 · 설계변경 승인 2026. 6. 15.).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="4" customHeight="1"/>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>제2조 (변경 내용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="43.5" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>위 표에 적은 바와 같이 계약 내용을 변경한다. 세부 내용은 별첨 변경 산출내역서에 따른다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="4" customHeight="1"/>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>제3조 (변경 후 계약금액)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="43.5" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>변경 후 계약금액은 위 표에 적은 금액으로 하며, 그 밖의 사항은 당초 계약에 따른다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="4" customHeight="1"/>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>제4조 (공사기간)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="43.5" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>공사기간은 위 표에 적은 바와 같이 변경한다. 기간이 변경되지 아니하는 경우 당초 기간을 유지한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="4" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>제5조 (효력)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="29" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>이 변경계약에서 정하지 아니한 사항은 당초 계약의 내용에 따른다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="4" customHeight="1"/>
-    <row r="33" ht="6" customHeight="1"/>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>이 변경계약을 증명하기 위하여 2통을 작성하여 갑과 을이 각각 기명날인한 후 1통씩 보관한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="6" customHeight="1"/>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>상호(성명)</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>사업자등록번호</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t>대표자</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="8" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="P36" s="5" t="n"/>
-      <c r="Q36" s="5" t="n"/>
-      <c r="R36" s="5" t="n"/>
-      <c r="S36" s="5" t="n"/>
-      <c r="T36" s="5" t="n"/>
-      <c r="U36" s="5" t="n"/>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="n"/>
-      <c r="X36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>갑</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>가나시</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="17" t="inlineStr">
-        <is>
-          <t>가나시장</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="5" t="n"/>
-      <c r="O37" s="9" t="inlineStr">
-        <is>
-          <t>가나시 시청로 1</t>
-        </is>
-      </c>
-      <c r="P37" s="5" t="n"/>
-      <c r="Q37" s="5" t="n"/>
-      <c r="R37" s="5" t="n"/>
-      <c r="S37" s="5" t="n"/>
-      <c r="T37" s="5" t="n"/>
-      <c r="U37" s="5" t="n"/>
-      <c r="V37" s="17" t="inlineStr">
-        <is>
-          <t>000-000-0000</t>
-        </is>
-      </c>
-      <c r="W37" s="5" t="n"/>
-      <c r="X37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>을</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="17" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
-      <c r="L38" s="17" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="n"/>
-      <c r="N38" s="5" t="n"/>
-      <c r="O38" s="9" t="inlineStr">
-        <is>
-          <t>가나시 마바로 45, 2층</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="n"/>
-      <c r="Q38" s="5" t="n"/>
-      <c r="R38" s="5" t="n"/>
-      <c r="S38" s="5" t="n"/>
-      <c r="T38" s="5" t="n"/>
-      <c r="U38" s="5" t="n"/>
-      <c r="V38" s="17" t="inlineStr">
-        <is>
-          <t>000-000-0000</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="n"/>
-      <c r="X38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="6" customHeight="1"/>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="6" customHeight="1"/>
-    <row r="42" ht="10" customHeight="1"/>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="18" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="19" t="inlineStr"/>
-      <c r="K44" s="20" t="inlineStr">
-        <is>
-          <t>갑 (발주자·원사업자)</t>
-        </is>
-      </c>
-      <c r="Q44" s="21" t="inlineStr">
-        <is>
-          <t>가나시장</t>
-        </is>
-      </c>
-      <c r="U44" s="22" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="19" t="inlineStr"/>
-      <c r="K45" s="20" t="inlineStr">
-        <is>
-          <t>을 (수급인·수급사업자)</t>
-        </is>
-      </c>
-      <c r="Q45" s="21" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="U45" s="22" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="6" customHeight="1"/>
-    <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="23" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="M10:R10"/>
-    <mergeCell ref="S14:X14"/>
-    <mergeCell ref="A16:X16"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="K44:P44"/>
-    <mergeCell ref="A25:X25"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="M13:R13"/>
-    <mergeCell ref="S13:X13"/>
-    <mergeCell ref="Q45:T45"/>
-    <mergeCell ref="M11:R11"/>
-    <mergeCell ref="M12:R12"/>
-    <mergeCell ref="A18:X18"/>
-    <mergeCell ref="A27:X27"/>
-    <mergeCell ref="O38:U38"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="A21:X21"/>
-    <mergeCell ref="S10:X10"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="V36:X36"/>
-    <mergeCell ref="O37:U37"/>
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="U44:X44"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="A22:X22"/>
-    <mergeCell ref="A45:J45"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="M14:R14"/>
-    <mergeCell ref="O36:U36"/>
-    <mergeCell ref="U45:X45"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A43:X43"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="V37:X37"/>
-    <mergeCell ref="A28:X28"/>
-    <mergeCell ref="A19:X19"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="G8:X8"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="A31:X31"/>
-    <mergeCell ref="A40:X40"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="S12:X12"/>
-    <mergeCell ref="A30:X30"/>
-    <mergeCell ref="A34:X34"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="V38:X38"/>
-    <mergeCell ref="A48:X48"/>
-    <mergeCell ref="A24:X24"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="K45:P45"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="Q44:T44"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="S11:X11"/>
-    <mergeCell ref="H37:K37"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/gy-byeongyeong.xlsx
+++ b/web/public/forms/gy-byeongyeong.xlsx
@@ -605,7 +605,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
